--- a/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
+++ b/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\FlowchartTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02D49E3-5D13-434B-B209-DC6EABB26415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35103690-0482-44AA-9245-672E62EAE6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="111">
   <si>
     <t>Name</t>
   </si>
@@ -366,6 +366,22 @@
 "TOms":{"VShort":2000, "Short":4000, "Medium":16000, "Long":64000, "VLong":256000},
 "DEL":{"D1":1, "D2":2, "D3":3, "D4":4, "D6":6, "WaitForQueue":45},
 "RS":{"DeleteFiles":{"NR":3, "TS":4}, "ExcelReportProcess":{"NR":3, "TS":6}, "OutlookGetEmails":{"NR":3, "TS":8}, "AppXYLogin":{"NR":2, "TS":6}, "EdgeLoadingPage":{"NR":9, "TS":3}},
+"SE":["SE00: Critical error while reading Config file.", 
+"SE01: Critical error while initializing the environment.", 
+"SE02: Unexpected system exception."], 
+"AE":["AE00: Robot couldn't open Excel input file: {0}, sheet: {1}.", 
+"AE01: Robot couldn't login to AppXY.", 
+"AE02: Robot couldn't logout from AppXY."], 
+"BE":["BE00: No input data found in: {0} to process.", 
+"BE01: Missing required column in: {0}.", 
+"BE02: Some data isn't correct. Moving to next transaction."],
+"Status": ["OK", "Błąd - wprowadź pozycję ręcznie", "Błąd - brakujące\\niepoprawne dane do wprowadzenia: {0}"]}</t>
+  </si>
+  <si>
+    <t>{"TO":{"VShort":2, "Short":4, "Medium":16, "Long":64, "VLong":256},
+"TOms":{"VShort":2000, "Short":4000, "Medium":16000, "Long":64000, "VLong":256000},
+"DEL":{"D1":1, "D2":2, "D3":3, "D4":4, "D6":6, "WaitForQueue":45},
+"RS":{"DeleteFiles":{"NR":3, "TS":4}, "ExcelReportProcess":{"NR":3, "TS":12}, "OutlookGetEmails":{"NR":3, "TS":8}, "AppXYLogin":{"NR":2, "TS":6}, "EdgeLoadingPage":{"NR":9, "TS":3}},
 "SE":["SE00: Critical error while reading Config file.", 
 "SE01: Critical error while initializing the environment.", 
 "SE02: Unexpected system exception."], 
@@ -750,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -1024,14 +1040,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
     </row>

--- a/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
+++ b/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\FlowchartTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE27B71-42CC-4CCB-8B9B-2D59ABE1837A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924E14A7-6024-4EA7-8A63-B3335A019764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -369,10 +369,16 @@
 Pozdrawiam,&lt;br&gt;Robot&lt;br&gt;Mail: &lt;varEmailAddress&gt;&lt;br&gt;</t>
   </si>
   <si>
+    <t>{"Col1": "Kolumna1", "Col2": "Kolumna2", "Col3": "Kolumna3", "Status": "STATUS"}</t>
+  </si>
+  <si>
+    <t>Dictionary with mandatory columns when working with an Excel input file, where key: name of the column used in Workflows (OpenApplications, ExcelGetInputCases and SendEmailBusiness), value: corresponding column name from the input file.</t>
+  </si>
+  <si>
     <t>{"TO":{"VShort":2, "Short":4, "Medium":16, "Long":64, "VLong":256},
 "TOms":{"VShort":2000, "Short":4000, "Medium":16000, "Long":64000, "VLong":256000},
 "DEL":{"D1":1, "D2":2, "D3":3, "D4":4, "D6":6, "WaitForQueue":45},
-"RS":{"FoldersCreateDelete":{"NR":3, "TS":4}, "ExcelReportProcess":{"NR":3, "TS":6}, "OutlookGetEmails":{"NR":3, "TS":8}, "AppXYLogin":{"NR":2, "TS":6}, "EdgeLoadingPage":{"NR":9, "TS":3}},
+"RS":{"FoldersCreateDelete":{"NR":3, "TS":4}, "ExcelReportProcess":{"NR":3, "TS":6}, "OutlookGetEmails":{"NR":3, "TS":8}, "OutlookSendEmail":{"NR":3, "TS":6}, "AppXYLogin":{"NR":2, "TS":6}, "EdgeLoadingPage":{"NR":9, "TS":3}},
 "SE":["SE00: Critical error while reading Config file.", 
 "SE01: Critical error while initializing the environment."], 
 "AE":["AE00: Unexpected system exception.", 
@@ -380,12 +386,6 @@
 "AE02: Robot couldn't logout from AppXY."], 
 "BE":["BE00: No input data found in: {0} to process."],
 "Status": ["OK", "Błąd - wprowadź pozycję ręcznie."]}</t>
-  </si>
-  <si>
-    <t>{"Col1": "Kolumna1", "Col2": "Kolumna2", "Col3": "Kolumna3", "Status": "STATUS"}</t>
-  </si>
-  <si>
-    <t>Dictionary with mandatory columns when working with an Excel input file, where key: name of the column used in Workflows (OpenApplications, ExcelGetInputCases and SendEmailBusiness), value: corresponding column name from the input file.</t>
   </si>
 </sst>
 </file>
@@ -769,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1059,7 +1059,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1469,10 +1469,10 @@
         <v>100</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
+++ b/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\FlowchartTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924E14A7-6024-4EA7-8A63-B3335A019764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3AE9BC-5B4F-4F8E-979D-58D4AAB08112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="114">
   <si>
     <t>Name</t>
   </si>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>E-mail body for process fatal exception.</t>
-  </si>
-  <si>
-    <t>Process_Name_Test_Outlook_Robot</t>
   </si>
   <si>
     <t>E-mail credentials asset name in Orchestrator for Outlook-Robot account.</t>
@@ -386,6 +383,12 @@
 "AE02: Robot couldn't logout from AppXY."], 
 "BE":["BE00: No input data found in: {0} to process."],
 "Status": ["OK", "Błąd - wprowadź pozycję ręcznie."]}</t>
+  </si>
+  <si>
+    <t>Process_Name_Outlook_Robot</t>
+  </si>
+  <si>
+    <t>Process_Name_Outlook_Robot_Test</t>
   </si>
 </sst>
 </file>
@@ -769,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -780,7 +783,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
         <v>53</v>
@@ -824,10 +827,10 @@
         <v>57</v>
       </c>
       <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" t="s">
         <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -857,7 +860,7 @@
         <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
         <v>73</v>
@@ -879,10 +882,10 @@
         <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -893,7 +896,7 @@
         <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -901,10 +904,10 @@
         <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -915,7 +918,7 @@
         <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -923,7 +926,7 @@
         <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
         <v>78</v>
@@ -934,7 +937,7 @@
         <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
         <v>80</v>
@@ -945,10 +948,10 @@
         <v>81</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -964,7 +967,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
         <v>84</v>
@@ -975,10 +978,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" t="s">
         <v>108</v>
-      </c>
-      <c r="B31" t="s">
-        <v>109</v>
       </c>
       <c r="C31" t="s">
         <v>86</v>
@@ -986,24 +989,24 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" t="s">
         <v>96</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1059,7 +1062,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1070,7 +1073,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
         <v>53</v>
@@ -1114,10 +1117,10 @@
         <v>57</v>
       </c>
       <c r="B12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" t="s">
         <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1147,7 +1150,7 @@
         <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
         <v>73</v>
@@ -1169,10 +1172,10 @@
         <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1183,7 +1186,7 @@
         <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1191,10 +1194,10 @@
         <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1205,7 +1208,7 @@
         <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1213,7 +1216,7 @@
         <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
         <v>78</v>
@@ -1224,7 +1227,7 @@
         <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
         <v>80</v>
@@ -1238,7 +1241,7 @@
         <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -1254,7 +1257,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
         <v>84</v>
@@ -1265,10 +1268,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" t="s">
         <v>108</v>
-      </c>
-      <c r="B31" t="s">
-        <v>109</v>
       </c>
       <c r="C31" t="s">
         <v>86</v>
@@ -1276,24 +1279,24 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" t="s">
         <v>96</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1466,13 +1469,13 @@
     </row>
     <row r="21" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
+++ b/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\FlowchartTemplateC#\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Piotr\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\FlowchartTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441C4230-87BA-4C3F-A868-38CB5A7BA091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D4AD7-CCF2-4EF9-B5B1-068D901D9258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings_Prod" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="124">
   <si>
     <t>Name</t>
   </si>
@@ -212,9 +212,6 @@
   </si>
   <si>
     <t>E-mail domain (Exchange).</t>
-  </si>
-  <si>
-    <t>E-mail server (Exchange).</t>
   </si>
   <si>
     <t>EmailTo_BusinessException01</t>
@@ -398,6 +395,86 @@
   </si>
   <si>
     <t>Folder path for text file with Robot operating status indicator.</t>
+  </si>
+  <si>
+    <t>Cześć,&lt;br&gt;&lt;br&gt;
+zakończyłem proces: {0}. {1}.&lt;br&gt;&lt;br&gt;
+Jeśli jest potrzeba zmiany adresata, prosimy o zgłoszenie przez SD.&lt;br&gt;
+Wiadomość została wygenerowana automatycznie prosimy na nią nie odpowiadać.&lt;br&gt;&lt;br&gt;
+Pozdrawiam,&lt;br&gt;
+Robot&lt;br&gt;
+Mail: &lt;varEmailAddress&gt;&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Uwaga,&lt;br&gt;&lt;br&gt;
+miałem problem podczas inicjalizacji środowiska do pracy w związku z czym zatrzymałem swoje działanie.&lt;br&gt;
+Sprawdź proszę poprawność działania środowiska i uruchom mnie ponownie.&lt;br&gt;&lt;br&gt;
+{0}&lt;br&gt;&lt;br&gt;
+Pozdrawiam,&lt;br&gt;
+Robot&lt;br&gt;
+Mail: &lt;varEmailAddress&gt;&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Uwaga,&lt;br&gt;&lt;br&gt;
+napotkałem niepokojącą ilość błędów systemowych w związku z czym zatrzymałem swoje działanie.&lt;br&gt;
+Sprawdź proszę poprawność działania środowiska i uruchom mnie ponownie.&lt;br&gt;&lt;br&gt;
+{0}&lt;br&gt;&lt;br&gt;
+Pozdrawiam,&lt;br&gt;
+Robot&lt;br&gt;
+Mail: &lt;varEmailAddress&gt;&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Cześć,&lt;br&gt;&lt;br&gt;
+poniższa transakcja nie została zweryfikowana w systemie XYZ: {0}. &lt;br&gt;&lt;br&gt;
+{1}&lt;br&gt;&lt;br&gt;
+Jeśli jest potrzeba zmiany adresata, prosimy o zgłoszenie przez SD.&lt;br&gt;
+Wiadomość została wygenerowana automatycznie prosimy na nią nie odpowiadać.&lt;br&gt;&lt;br&gt;
+Pozdrawiam,&lt;br&gt;
+Robot&lt;br&gt;
+Mail: &lt;varEmailAddress&gt;&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>EmailBodyTable</t>
+  </si>
+  <si>
+    <t>E-mail body table with error details.</t>
+  </si>
+  <si>
+    <t>&lt;table caption="Tabela z błędem"; style="width:80%; background-color:#D3D3D3; font-family:verdana; color:black; border:4px solid #E6E6E6; border-collapse:collapse; word-break: break-word;"&gt;
+&lt;tr&gt;
+&lt;th colspan="2"; align="left"; style="height:2em; background-color:#F0BE0E; padding:10px; font-size:1.4em"&gt;
+&amp;#9888 Wystąpił błąd &lt;varAppOrBusi&gt;
+&lt;/th&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td style="width:20%; padding:10px; font-weight:bold;"&gt;
+Błąd:
+&lt;/td&gt;
+&lt;td style="padding-left:10px; color:green;"&gt;
+&lt;pre style="font-family:verdana; white-space: pre-wrap;"&gt;
+&lt;varErrorMsg&gt;
+&lt;/pre&gt;&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td style="padding:10px; font-weight:bold;"&gt;
+Źródło:
+&lt;/td&gt;
+&lt;td style="padding-left:10px; color:green;"&gt;
+&lt;varErrorSource&gt;
+&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td colspan="2"; align="center"; style="font-size:0.7em;"&gt;
+To jest automatyczna wiadomość, proszę na nią nie odpowiadać.
+&lt;/td&gt;
+&lt;/tr&gt;
+&lt;/table&gt;</t>
+  </si>
+  <si>
+    <t>smtp.gmail.com</t>
+  </si>
+  <si>
+    <t>E-mail server (Exchange or SMTP).</t>
   </si>
 </sst>
 </file>
@@ -448,11 +525,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -734,7 +810,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Arkusz1"/>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="50.77734375" customWidth="1"/>
@@ -779,7 +855,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -790,7 +866,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
         <v>53</v>
@@ -812,7 +888,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -834,10 +910,10 @@
         <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -859,161 +935,172 @@
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
         <v>72</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17">
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
         <v>77</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" t="s">
         <v>79</v>
-      </c>
-      <c r="B25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
         <v>97</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1024,7 +1111,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71EB2DDF-63F3-4379-B0C3-3AFA21562EA7}">
   <sheetPr codeName="Arkusz2"/>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="50.77734375" customWidth="1"/>
@@ -1047,7 +1134,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -1058,7 +1145,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -1069,7 +1156,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1080,7 +1167,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
         <v>53</v>
@@ -1102,7 +1189,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -1113,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -1124,10 +1211,10 @@
         <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1146,164 +1233,175 @@
         <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
         <v>72</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17">
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
         <v>77</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
         <v>79</v>
-      </c>
-      <c r="B25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" t="s">
         <v>106</v>
       </c>
-      <c r="B30" t="s">
-        <v>107</v>
-      </c>
       <c r="C30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
         <v>97</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1357,7 +1455,7 @@
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
@@ -1366,24 +1464,24 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
         <v>114</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
         <v>66</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1478,7 +1576,7 @@
       <c r="A19" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="3" t="b">
+      <c r="B19" t="b">
         <v>1</v>
       </c>
       <c r="C19" t="s">
@@ -1487,13 +1585,13 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" t="s">
         <v>112</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
+++ b/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Piotr\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\FlowchartTemplateC#\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\FlowchartTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D4AD7-CCF2-4EF9-B5B1-068D901D9258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4460D97-21E6-4DDB-BF11-50354B746179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings_Prod" sheetId="1" r:id="rId1"/>
@@ -440,41 +440,41 @@
     <t>E-mail body table with error details.</t>
   </si>
   <si>
-    <t>&lt;table caption="Tabela z błędem"; style="width:80%; background-color:#D3D3D3; font-family:verdana; color:black; border:4px solid #E6E6E6; border-collapse:collapse; word-break: break-word;"&gt;
+    <t>smtp.gmail.com</t>
+  </si>
+  <si>
+    <t>E-mail server (Exchange or SMTP).</t>
+  </si>
+  <si>
+    <t>&lt;table style="width:80%; max-width:700px; background-color:#f5f5f5; font-family:Verdana, Arial, sans-serif; color:#333; border:1px solid #ddd; border-collapse:collapse;"&gt;
 &lt;tr&gt;
-&lt;th colspan="2"; align="left"; style="height:2em; background-color:#F0BE0E; padding:10px; font-size:1.4em"&gt;
-&amp;#9888 Wystąpił błąd &lt;varAppOrBusi&gt;
-&lt;/th&gt;
-&lt;/tr&gt;
-&lt;tr&gt;
-&lt;td style="width:20%; padding:10px; font-weight:bold;"&gt;
-Błąd:
-&lt;/td&gt;
-&lt;td style="padding-left:10px; color:green;"&gt;
-&lt;pre style="font-family:verdana; white-space: pre-wrap;"&gt;
-&lt;varErrorMsg&gt;
-&lt;/pre&gt;&lt;/td&gt;
-&lt;/tr&gt;
-&lt;tr&gt;
-&lt;td style="padding:10px; font-weight:bold;"&gt;
-Źródło:
-&lt;/td&gt;
-&lt;td style="padding-left:10px; color:green;"&gt;
-&lt;varErrorSource&gt;
+&lt;td colspan="2" style="background-color:#F0BE0E; padding:14px; font-size:18px; font-weight:bold;"&gt;
+⚠ Wystąpił błąd {{varAppOrBusi}}
 &lt;/td&gt;
 &lt;/tr&gt;
 &lt;tr&gt;
-&lt;td colspan="2"; align="center"; style="font-size:0.7em;"&gt;
-To jest automatyczna wiadomość, proszę na nią nie odpowiadać.
+&lt;td style="width:10%; padding:12px; padding-right:0px; font-weight:bold; border-top:1px solid #ddd;"&gt;
+Błąd:
+&lt;/td&gt;
+&lt;td style="padding:12px; padding-left:20px; border-top:1px solid #ddd; color:#006400;"&gt;
+&lt;pre style="margin:0; font-family:Consolas, monospace; font-size:18px; white-space:pre-wrap;"&gt;{{varErrorMsg}}
+&lt;/pre&gt;
+&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td style="padding:12px; padding-right:0px; font-weight:bold; border-top:1px solid #ddd;"&gt;
+Źródło:
+&lt;/td&gt;
+&lt;td style="padding:12px; padding-left:20px; border-top:1px solid #ddd; color:#006400;"&gt;
+{{varErrorSource}}
+&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td colspan="2" style="padding:10px; font-size:11px; color:#777; text-align:center; border-top:1px solid #ddd;"&gt;
+To jest automatyczna wiadomość systemowa — proszę na nią nie odpowiadać.
 &lt;/td&gt;
 &lt;/tr&gt;
 &lt;/table&gt;</t>
-  </si>
-  <si>
-    <t>smtp.gmail.com</t>
-  </si>
-  <si>
-    <t>E-mail server (Exchange or SMTP).</t>
   </si>
 </sst>
 </file>
@@ -935,7 +935,7 @@
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1075,7 +1075,7 @@
         <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
         <v>120</v>
@@ -1233,10 +1233,10 @@
         <v>59</v>
       </c>
       <c r="B14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
         <v>122</v>
-      </c>
-      <c r="C14" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1376,7 +1376,7 @@
         <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
         <v>120</v>

--- a/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
+++ b/FlowchartTemplateC#/Data/Config_Process_Name.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\FlowchartTemplateC#\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PiotrDane\02 Programowanie\05 UiPath\02 Projekty\PG-RPA\FlowchartTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4460D97-21E6-4DDB-BF11-50354B746179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08827215-1790-474B-9DF7-3F334A3022DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,32 +446,37 @@
     <t>E-mail server (Exchange or SMTP).</t>
   </si>
   <si>
-    <t>&lt;table style="width:80%; max-width:700px; background-color:#f5f5f5; font-family:Verdana, Arial, sans-serif; color:#333; border:1px solid #ddd; border-collapse:collapse;"&gt;
+    <t>&lt;table style="width:80%; background-color:#f5f5f5; font-family:Verdana, Arial, sans-serif; color:#333; border:1px solid #ddd; border-collapse:collapse;"&gt;
 &lt;tr&gt;
 &lt;td colspan="2" style="background-color:#F0BE0E; padding:14px; font-size:18px; font-weight:bold;"&gt;
+&lt;!--Header--&gt;
 ⚠ Wystąpił błąd {{varAppOrBusi}}
 &lt;/td&gt;
 &lt;/tr&gt;
 &lt;tr&gt;
-&lt;td style="width:10%; padding:12px; padding-right:0px; font-weight:bold; border-top:1px solid #ddd;"&gt;
+&lt;td style="width:10%; padding:12px; padding-right:0px; font-weight:bold; border-bottom:1px solid #ddd;"&gt;
 Błąd:
 &lt;/td&gt;
-&lt;td style="padding:12px; padding-left:20px; border-top:1px solid #ddd; color:#006400;"&gt;
-&lt;pre style="margin:0; font-family:Consolas, monospace; font-size:18px; white-space:pre-wrap;"&gt;{{varErrorMsg}}
+&lt;td style="padding:12px; padding-left:20px; border-bottom:1px solid #ddd; color:#006400;"&gt;
+&lt;!--Error msg--&gt;
+&lt;pre style="margin:0; font-family:Consolas, monospace; font-size:18px; white-space:pre-wrap; width:500px; overflow:auto;"&gt;
+{{varErrorMsg}}
 &lt;/pre&gt;
 &lt;/td&gt;
 &lt;/tr&gt;
 &lt;tr&gt;
-&lt;td style="padding:12px; padding-right:0px; font-weight:bold; border-top:1px solid #ddd;"&gt;
+&lt;td style="padding:12px; padding-right:0px; font-weight:bold; border-bottom:1px solid #ddd;"&gt;
 Źródło:
 &lt;/td&gt;
-&lt;td style="padding:12px; padding-left:20px; border-top:1px solid #ddd; color:#006400;"&gt;
+&lt;td style="padding:12px; padding-left:20px; border-bottom:1px solid #ddd; color:#006400;"&gt;
+&lt;!--Error src--&gt;
 {{varErrorSource}}
 &lt;/td&gt;
 &lt;/tr&gt;
 &lt;tr&gt;
-&lt;td colspan="2" style="padding:10px; font-size:11px; color:#777; text-align:center; border-top:1px solid #ddd;"&gt;
-To jest automatyczna wiadomość systemowa — proszę na nią nie odpowiadać.
+&lt;td colspan="2" style="padding:10px; font-size:11px; color:#777; text-align:center; border-bottom:1px solid #ddd;"&gt;
+&lt;!--Footer--&gt;
+To jest automatyczna wiadomość — proszę na nią nie odpowiadać.
 &lt;/td&gt;
 &lt;/tr&gt;
 &lt;/table&gt;</t>
